--- a/public/Master Brand.xlsx
+++ b/public/Master Brand.xlsx
@@ -44,10 +44,10 @@
     <t>Brand Gender</t>
   </si>
   <si>
-    <t>KOH001</t>
-  </si>
-  <si>
-    <t>B00001</t>
+    <t>BYR000000001</t>
+  </si>
+  <si>
+    <t>BRN000000001</t>
   </si>
   <si>
     <t>C&amp;B</t>
@@ -56,22 +56,22 @@
     <t>Mens</t>
   </si>
   <si>
-    <t>B00002</t>
+    <t>BRN000000002</t>
   </si>
   <si>
     <t>APT9/MENS</t>
   </si>
   <si>
-    <t>B00003</t>
+    <t>BRN000000003</t>
   </si>
   <si>
     <t>JB</t>
   </si>
   <si>
-    <t>ON001</t>
-  </si>
-  <si>
-    <t>B00004</t>
+    <t>BYR000000003</t>
+  </si>
+  <si>
+    <t>BRN000000004</t>
   </si>
   <si>
     <t>VMI - LADIES</t>
@@ -80,103 +80,103 @@
     <t>Ladies</t>
   </si>
   <si>
-    <t>JCP001</t>
-  </si>
-  <si>
-    <t>B00005</t>
+    <t>BYR000000002</t>
+  </si>
+  <si>
+    <t>BRN000000005</t>
   </si>
   <si>
     <t>SJB - PLUS</t>
   </si>
   <si>
-    <t>B00006</t>
+    <t>BRN000000006</t>
   </si>
   <si>
     <t>LADIES</t>
   </si>
   <si>
-    <t>B00007</t>
+    <t>BRN000000007</t>
   </si>
   <si>
     <t>GIRLS</t>
   </si>
   <si>
-    <t>MUJ001</t>
-  </si>
-  <si>
-    <t>B00008</t>
-  </si>
-  <si>
-    <t>Yarn dyed</t>
-  </si>
-  <si>
-    <t>LEV001</t>
-  </si>
-  <si>
-    <t>B00009</t>
+    <t>BYR000000004</t>
+  </si>
+  <si>
+    <t>BRN000000008</t>
+  </si>
+  <si>
+    <t>YARN DYED</t>
+  </si>
+  <si>
+    <t>BYR000000006</t>
+  </si>
+  <si>
+    <t>BRN000000009</t>
   </si>
   <si>
     <t>MENS</t>
   </si>
   <si>
-    <t>B00010</t>
-  </si>
-  <si>
-    <t>SJB - Missy</t>
-  </si>
-  <si>
-    <t>B00011</t>
-  </si>
-  <si>
-    <t>SJB - Petite</t>
-  </si>
-  <si>
-    <t>B00012</t>
-  </si>
-  <si>
-    <t>SJB - Tall</t>
-  </si>
-  <si>
-    <t>B00013</t>
-  </si>
-  <si>
-    <t>SJB - Mama</t>
-  </si>
-  <si>
-    <t>B00014</t>
-  </si>
-  <si>
-    <t>SJB - Missy - ADP</t>
-  </si>
-  <si>
-    <t>B00015</t>
-  </si>
-  <si>
-    <t>SJB - Mama - ADP</t>
-  </si>
-  <si>
-    <t>B00016</t>
-  </si>
-  <si>
-    <t>SJB - Missy - CVC</t>
-  </si>
-  <si>
-    <t>B00017</t>
-  </si>
-  <si>
-    <t>Ladies mock nk</t>
-  </si>
-  <si>
-    <t>B00018</t>
-  </si>
-  <si>
-    <t>Ladies turtle nk</t>
-  </si>
-  <si>
-    <t>B00019</t>
-  </si>
-  <si>
-    <t>J.Beans</t>
+    <t>BRN000000010</t>
+  </si>
+  <si>
+    <t>SJB - MISSY</t>
+  </si>
+  <si>
+    <t>BRN000000011</t>
+  </si>
+  <si>
+    <t>SJB - PETITE</t>
+  </si>
+  <si>
+    <t>BRN000000012</t>
+  </si>
+  <si>
+    <t>SJB - TALL</t>
+  </si>
+  <si>
+    <t>BRN000000013</t>
+  </si>
+  <si>
+    <t>SJB - MAMA</t>
+  </si>
+  <si>
+    <t>BRN000000014</t>
+  </si>
+  <si>
+    <t>SJB - MISSY - ADP</t>
+  </si>
+  <si>
+    <t>BRN000000015</t>
+  </si>
+  <si>
+    <t>SJB - MAMA - ADP</t>
+  </si>
+  <si>
+    <t>BRN000000016</t>
+  </si>
+  <si>
+    <t>SJB - MISSY - CVC</t>
+  </si>
+  <si>
+    <t>BRN000000017</t>
+  </si>
+  <si>
+    <t>LADIES MOCK NK</t>
+  </si>
+  <si>
+    <t>BRN000000018</t>
+  </si>
+  <si>
+    <t>LADIES TURTLE NK</t>
+  </si>
+  <si>
+    <t>BRN000000019</t>
+  </si>
+  <si>
+    <t>J.BEANS</t>
   </si>
 </sst>
 </file>
@@ -189,13 +189,19 @@
     <numFmt numFmtId="178" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="179" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -660,140 +666,142 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1116,7 +1124,11 @@
   <dimension ref="A1:E20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="9" style="1"/>
+    <col min="2" max="2" width="14.2857142857143" style="1" customWidth="1"/>
+    <col min="3" max="3" width="14.8571428571429" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.5714285714286" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1143,10 +1155,10 @@
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E2" s="1" t="s">
@@ -1160,10 +1172,10 @@
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E3" s="1" t="s">
@@ -1177,10 +1189,10 @@
       <c r="B4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E4" s="1" t="s">
@@ -1194,10 +1206,10 @@
       <c r="B5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E5" s="1" t="s">
@@ -1211,10 +1223,10 @@
       <c r="B6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="2" t="s">
         <v>19</v>
       </c>
       <c r="E6" s="1" t="s">
@@ -1228,10 +1240,10 @@
       <c r="B7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="2" t="s">
         <v>21</v>
       </c>
       <c r="E7" s="1" t="s">
@@ -1245,10 +1257,10 @@
       <c r="B8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E8" s="1" t="s">
@@ -1262,10 +1274,10 @@
       <c r="B9" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E9" s="1" t="s">
@@ -1279,10 +1291,10 @@
       <c r="B10" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="2" t="s">
         <v>29</v>
       </c>
       <c r="E10" s="1" t="s">
@@ -1296,10 +1308,10 @@
       <c r="B11" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E11" s="1" t="s">
@@ -1313,10 +1325,10 @@
       <c r="B12" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E12" s="1" t="s">
@@ -1330,10 +1342,10 @@
       <c r="B13" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="2" t="s">
         <v>35</v>
       </c>
       <c r="E13" s="1" t="s">
@@ -1347,10 +1359,10 @@
       <c r="B14" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="2" t="s">
         <v>37</v>
       </c>
       <c r="E14" s="1" t="s">
@@ -1364,10 +1376,10 @@
       <c r="B15" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" s="2" t="s">
         <v>39</v>
       </c>
       <c r="E15" s="1" t="s">
@@ -1381,10 +1393,10 @@
       <c r="B16" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" s="2" t="s">
         <v>41</v>
       </c>
       <c r="E16" s="1" t="s">
@@ -1398,10 +1410,10 @@
       <c r="B17" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" s="2" t="s">
         <v>43</v>
       </c>
       <c r="E17" s="1" t="s">
@@ -1415,10 +1427,10 @@
       <c r="B18" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D18" s="2" t="s">
         <v>45</v>
       </c>
       <c r="E18" s="1" t="s">
@@ -1432,10 +1444,10 @@
       <c r="B19" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" s="2" t="s">
         <v>47</v>
       </c>
       <c r="E19" s="1" t="s">
@@ -1449,10 +1461,10 @@
       <c r="B20" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D20" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E20" s="1" t="s">
